--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487688_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487688_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8325</v>
+        <v>3.2013</v>
       </c>
       <c r="E2" t="n">
-        <v>3.288</v>
+        <v>2.1474</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5445</v>
+        <v>1.0539</v>
       </c>
       <c r="G2" t="n">
         <v>3.0697</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5105</v>
+        <v>0.8793</v>
       </c>
       <c r="T2" t="n">
-        <v>1.495</v>
+        <v>0.3544</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0155</v>
+        <v>0.5249</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7062</v>
+        <v>1.3246</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8741</v>
+        <v>-0.4737</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5803</v>
+        <v>1.7984</v>
       </c>
       <c r="G3" t="n">
         <v>4.8196</v>
@@ -688,13 +688,13 @@
         <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.679</v>
+        <v>-0.0606</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8838</v>
+        <v>-0.4834</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2048</v>
+        <v>0.4229</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3299</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6665</v>
+        <v>-0.5753</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2792</v>
+        <v>-0.079</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3873</v>
+        <v>-0.4963</v>
       </c>
       <c r="G4" t="n">
         <v>1.172</v>
@@ -766,13 +766,13 @@
         <v>0.5821</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0361</v>
+        <v>0.1273</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.157</v>
+        <v>0.0432</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1932</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5164</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VILASANCHEZ FREIJOMIL</t>
+          <t>A. OLMEDO VELASCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.524</v>
+        <v>-1.3597</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1795</v>
+        <v>-2.9768</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3445</v>
+        <v>1.6172</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8088</v>
+        <v>-3.1042</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6698</v>
+        <v>-3.3589</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.139</v>
+        <v>0.2547</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0206</v>
+        <v>-2.5892</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0206</v>
+        <v>-2.5993</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.0101</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8294</v>
+        <v>-0.515</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6904</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.139</v>
+        <v>0.2447</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3881</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5821</v>
+        <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3271</v>
+        <v>-0.1211</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2299</v>
+        <v>0.0751</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.1962</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. PEREZ BERNABEU</t>
+          <t>J. VILASANCHEZ FREIJOMIL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.735</v>
+        <v>-1.3694</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4536</v>
+        <v>-1.0794</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2814</v>
+        <v>-0.29</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3276</v>
+        <v>-0.8088</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1055</v>
+        <v>-0.6698</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4331</v>
+        <v>-0.139</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1142</v>
+        <v>0.0206</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3707</v>
+        <v>0.0206</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7435</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2134</v>
+        <v>-0.8294</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4762</v>
+        <v>-0.6904</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6896</v>
+        <v>-0.139</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3582</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1045</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2912</v>
+        <v>-0.1724</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3174</v>
+        <v>-0.1298</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0262</v>
+        <v>-0.0426</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. OLMEDO VELASCO</t>
+          <t>J. LOBATO ANDRADE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8206</v>
+        <v>-1.9252</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.4378</v>
+        <v>-2.3494</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6172</v>
+        <v>0.4242</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.1042</v>
+        <v>0.5415</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.3589</v>
+        <v>-0.7464</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2547</v>
+        <v>1.288</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.5892</v>
+        <v>0.3494</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.5993</v>
+        <v>0.1236</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0101</v>
+        <v>0.2258</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.515</v>
+        <v>0.1921</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.87</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2447</v>
+        <v>1.0622</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5821</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9105</v>
+        <v>-2.1344</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3284</v>
+        <v>1.3582</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5821</v>
+        <v>0.1452</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3859</v>
+        <v>-0.1868</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1962</v>
+        <v>0.332</v>
       </c>
       <c r="V7" t="n">
-        <v>2.4477</v>
+        <v>-1.8358</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4477</v>
+        <v>-0.3776</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.4582</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. LOBATO ANDRADE</t>
+          <t>E. PEREZ BERNABEU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8885</v>
+        <v>-1.9291</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1492</v>
+        <v>-1.5932</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2607</v>
+        <v>-0.3359</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5415</v>
+        <v>-1.3276</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7464</v>
+        <v>0.1055</v>
       </c>
       <c r="I8" t="n">
-        <v>1.288</v>
+        <v>-1.4331</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3494</v>
+        <v>-1.1142</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1236</v>
+        <v>-0.3707</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2258</v>
+        <v>-0.7435</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1921</v>
+        <v>-0.2134</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.87</v>
+        <v>0.4762</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0622</v>
+        <v>-0.6896</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7761</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1344</v>
+        <v>-3.1045</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3582</v>
+        <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1819</v>
+        <v>0.097</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0134</v>
+        <v>0.1777</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1685</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8358</v>
+        <v>0.6597</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3776</v>
+        <v>2.4477</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4582</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5161</v>
+        <v>-3.2826</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4669</v>
+        <v>-3.2062</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0491</v>
+        <v>-0.0764</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4269</v>
@@ -1156,13 +1156,13 @@
         <v>1.9403</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6249</v>
+        <v>-0.3914</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7134</v>
+        <v>-0.4526</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0612</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3299</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5501</v>
+        <v>-3.944</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6271</v>
+        <v>-3.2663</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.923</v>
+        <v>-0.6777</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6901</v>
@@ -1234,13 +1234,13 @@
         <v>1.9403</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4421</v>
+        <v>0.164</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4711</v>
+        <v>-0.1102</v>
       </c>
       <c r="U10" t="n">
-        <v>0.029</v>
+        <v>0.2743</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2239</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.1621</v>
+        <v>-9.859400000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.1794</v>
+        <v>-12.8766</v>
       </c>
       <c r="F11" t="n">
-        <v>3.017399999999999</v>
+        <v>3.0174</v>
       </c>
       <c r="G11" t="n">
         <v>1.245200000000001</v>
@@ -1282,7 +1282,7 @@
         <v>-5.5116</v>
       </c>
       <c r="I11" t="n">
-        <v>6.756900000000001</v>
+        <v>6.756899999999999</v>
       </c>
       <c r="J11" t="n">
         <v>4.325799999999999</v>
@@ -1291,13 +1291,13 @@
         <v>-1.2357</v>
       </c>
       <c r="L11" t="n">
-        <v>5.561499999999999</v>
+        <v>5.561500000000001</v>
       </c>
       <c r="M11" t="n">
         <v>-3.0807</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.276000000000001</v>
+        <v>-4.276</v>
       </c>
       <c r="O11" t="n">
         <v>1.1957</v>
@@ -1312,10 +1312,10 @@
         <v>14.5524</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3645</v>
+        <v>0.6673</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0153</v>
+        <v>-0.7124</v>
       </c>
       <c r="U11" t="n">
         <v>1.3799</v>
@@ -1324,7 +1324,7 @@
         <v>-2.0703</v>
       </c>
       <c r="W11" t="n">
-        <v>7.764000000000001</v>
+        <v>7.764</v>
       </c>
       <c r="X11" t="n">
         <v>-9.834200000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.220599999999999</v>
+        <v>9.5059</v>
       </c>
       <c r="E12" t="n">
-        <v>5.7536</v>
+        <v>5.8537</v>
       </c>
       <c r="F12" t="n">
-        <v>3.467</v>
+        <v>3.6521</v>
       </c>
       <c r="G12" t="n">
         <v>6.0112</v>
@@ -1390,13 +1390,13 @@
         <v>2.7164</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1631</v>
+        <v>0.4484</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0134</v>
+        <v>0.1135</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1497</v>
+        <v>0.3348</v>
       </c>
       <c r="V12" t="n">
         <v>0.3299</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6732</v>
+        <v>7.0046</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9658</v>
+        <v>3.8667</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7074</v>
+        <v>3.1379</v>
       </c>
       <c r="G13" t="n">
         <v>2.1032</v>
@@ -1468,13 +1468,13 @@
         <v>3.8806</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1763</v>
+        <v>0.155</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3201</v>
+        <v>-0.4192</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1438</v>
+        <v>0.5743</v>
       </c>
       <c r="V13" t="n">
         <v>1.8358</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0455</v>
+        <v>2.8349</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7749</v>
+        <v>-0.4273</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2706</v>
+        <v>3.2622</v>
       </c>
       <c r="G14" t="n">
         <v>1.9769</v>
@@ -1546,13 +1546,13 @@
         <v>2.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4746</v>
+        <v>1.264</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1684</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3062</v>
+        <v>0.2978</v>
       </c>
       <c r="V14" t="n">
         <v>0.5642</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. SHIELDS</t>
+          <t>T. VERDERA BENASSAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0663</v>
+        <v>1.4771</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8072</v>
+        <v>1.2077</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8735</v>
+        <v>0.2694</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5028</v>
+        <v>-0.4128</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0618</v>
+        <v>-0.2743</v>
       </c>
       <c r="I15" t="n">
-        <v>0.441</v>
+        <v>-0.1385</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5649</v>
+        <v>-0.4838</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6055</v>
+        <v>-1.174</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0406</v>
+        <v>0.6901</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0677</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6673</v>
+        <v>0.8996</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4004</v>
+        <v>-0.8286</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3881</v>
+        <v>2.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3881</v>
+        <v>3.8806</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1754</v>
+        <v>-0.0788</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2423</v>
+        <v>-0.0682</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4177</v>
+        <v>-0.0106</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.9418</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.7298</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-3.6716</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. VERDERA BENASSAR</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7858000000000001</v>
+        <v>1.3828</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1076</v>
+        <v>0.0119</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3218</v>
+        <v>1.3709</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4128</v>
+        <v>0.3715</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2743</v>
+        <v>1.5093</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1385</v>
+        <v>-1.1378</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4838</v>
+        <v>1.9308</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.174</v>
+        <v>2.1009</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6901</v>
+        <v>-0.1701</v>
       </c>
       <c r="M16" t="n">
-        <v>0.07099999999999999</v>
+        <v>-1.5592</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8996</v>
+        <v>-0.5916</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8286</v>
+        <v>-0.9677</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9105</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R16" t="n">
-        <v>3.8806</v>
+        <v>3.2985</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7701</v>
+        <v>-0.2902</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1683</v>
+        <v>-0.486</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6018</v>
+        <v>0.1957</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9418</v>
+        <v>1.8836</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7298</v>
+        <v>2.4477</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.6716</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>D. SHIELDS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4312</v>
+        <v>1.0846</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2884</v>
+        <v>-0.7071</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7196</v>
+        <v>1.7917</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3715</v>
+        <v>0.5028</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5093</v>
+        <v>0.0618</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1378</v>
+        <v>0.441</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9308</v>
+        <v>-0.5649</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1009</v>
+        <v>-0.6055</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1701</v>
+        <v>0.0406</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5592</v>
+        <v>1.0677</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5916</v>
+        <v>0.6673</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9677</v>
+        <v>0.4004</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8806</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2985</v>
+        <v>0.3881</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2418</v>
+        <v>0.1938</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7863</v>
+        <v>-0.1422</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4556</v>
+        <v>0.3359</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8836</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5251</v>
+        <v>-0.5796</v>
       </c>
       <c r="E18" t="n">
         <v>0.5318000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.057</v>
+        <v>-1.1115</v>
       </c>
       <c r="G18" t="n">
         <v>0.9084</v>
@@ -1858,13 +1858,13 @@
         <v>0.194</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1216</v>
+        <v>-0.1761</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1211</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0004</v>
+        <v>-0.055</v>
       </c>
       <c r="V18" t="n">
         <v>-1.506</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. MORENO GUTIERREZ</t>
+          <t>D. GARCIA DELGADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4286</v>
+        <v>-1.7364</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9284</v>
+        <v>-1.7212</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4997</v>
+        <v>-0.0152</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.1704</v>
+        <v>-2.0448</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3357</v>
+        <v>-0.0033</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8348</v>
+        <v>-2.0415</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0275</v>
+        <v>0.2371</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1493</v>
+        <v>0.7827</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1218</v>
+        <v>-0.5455</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1429</v>
+        <v>-2.282</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1864</v>
+        <v>-0.786</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9565</v>
+        <v>-1.496</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9403</v>
+        <v>0.7761</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4612</v>
+        <v>0.2397</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2412</v>
+        <v>-0.2807</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7023</v>
+        <v>0.5204</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6597</v>
+        <v>-0.7075</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6597</v>
+        <v>-0.7075</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. GARCIA DELGADO</t>
+          <t>F. MORENO GUTIERREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5273</v>
+        <v>-1.7378</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6211</v>
+        <v>-2.1286</v>
       </c>
       <c r="F20" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.3907</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0448</v>
+        <v>-3.1704</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0033</v>
+        <v>-2.3357</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0415</v>
+        <v>-0.8348</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2371</v>
+        <v>-1.0275</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7827</v>
+        <v>-1.1493</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5455</v>
+        <v>0.1218</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.282</v>
+        <v>-2.1429</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.786</v>
+        <v>-1.1864</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.496</v>
+        <v>-0.9565</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7761</v>
+        <v>1.9403</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4489</v>
+        <v>0.152</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1806</v>
+        <v>-0.4414</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6294</v>
+        <v>0.5933</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7075</v>
+        <v>-0.6597</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7075</v>
+        <v>-0.6597</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.34</v>
+        <v>-1.824</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.9819</v>
+        <v>-3.3813</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6418</v>
+        <v>1.5573</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0326</v>
@@ -2092,13 +2092,13 @@
         <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4134</v>
+        <v>0.1026</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9085</v>
+        <v>-0.3079</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4951</v>
+        <v>0.4105</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2821</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5245</v>
+        <v>-2.3638</v>
       </c>
       <c r="E22" t="n">
         <v>-0.8284</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6961</v>
+        <v>-1.5354</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1546</v>
@@ -2170,13 +2170,13 @@
         <v>0.194</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5639</v>
+        <v>-0.4032</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1817</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3822</v>
+        <v>-0.2215</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7148</v>
+        <v>-2.884</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6957</v>
+        <v>-5.2953</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9809</v>
+        <v>2.4113</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3038</v>
@@ -2248,13 +2248,13 @@
         <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8006</v>
+        <v>0.0303</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4116</v>
+        <v>-0.0112</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3889</v>
+        <v>0.0415</v>
       </c>
       <c r="V23" t="n">
         <v>1.5537</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.1623</v>
+        <v>12.1643</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0174</v>
+        <v>-3.017400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>13.1794</v>
+        <v>15.1814</v>
       </c>
       <c r="G24" t="n">
         <v>-1.245</v>
@@ -2296,7 +2296,7 @@
         <v>5.511499999999998</v>
       </c>
       <c r="I24" t="n">
-        <v>-6.7569</v>
+        <v>-6.756899999999999</v>
       </c>
       <c r="J24" t="n">
         <v>3.0807</v>
@@ -2326,22 +2326,22 @@
         <v>24.2538</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3644999999999993</v>
+        <v>1.6375</v>
       </c>
       <c r="T24" t="n">
         <v>-1.3799</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0153</v>
+        <v>3.0171</v>
       </c>
       <c r="V24" t="n">
         <v>2.0701</v>
       </c>
       <c r="W24" t="n">
-        <v>9.834100000000001</v>
+        <v>9.834099999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.764100000000001</v>
+        <v>-7.764099999999999</v>
       </c>
     </row>
   </sheetData>
